--- a/data/export/2026-10-05-operations.xlsx
+++ b/data/export/2026-10-05-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,17 +704,17 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -720,13 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1164,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1190,7 +1214,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1512,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1562,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1575,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1623,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1642,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1643,7 +1667,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1739,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,46 +1783,50 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1859,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1878,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1903,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,7 +2143,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,7 +2270,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2283,7 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2257,7 +2293,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2350,7 +2386,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2399,7 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2373,7 +2409,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2416,7 +2452,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2466,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,7 +2502,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2515,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2563,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2582,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,7 +2618,7 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2631,7 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2605,7 +2641,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2643,12 +2679,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2698,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2734,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2795,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2814,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2850,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2911,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2930,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2966,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3027,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3046,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3082,2819 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-operations.xlsx
+++ b/data/export/2026-10-05-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1131,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1164,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1188,33 +1200,37 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1247,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1280,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1304,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1396,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -1479,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1512,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1536,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1595,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1628,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1652,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1744,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1768,17 +1820,17 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1788,17 +1840,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1903,7 +1955,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1984,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2023,7 +2075,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2038,7 +2090,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2148,13 +2200,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2277,28 +2333,28 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2331,12 +2387,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2350,7 +2406,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2375,46 +2431,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2447,12 +2507,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2466,7 +2526,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2491,46 +2551,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2563,12 +2627,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2582,7 +2646,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2607,46 +2671,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2679,12 +2747,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2698,7 +2766,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2723,46 +2791,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2795,12 +2867,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2814,7 +2886,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2839,46 +2911,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2911,12 +2987,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2930,7 +3006,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2955,46 +3031,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3027,12 +3107,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3046,7 +3126,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3071,18 +3151,22 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3095,60 +3179,64 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3162,7 +3250,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3172,33 +3260,37 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3211,60 +3303,64 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3278,7 +3374,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3288,33 +3384,37 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3327,60 +3427,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3394,7 +3498,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3404,17 +3508,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3424,13 +3528,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3551,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3453,7 +3561,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3491,12 +3599,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3510,7 +3618,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3546,7 +3654,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3667,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3569,7 +3677,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3579,40 +3687,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3626,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3636,33 +3748,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3675,22 +3791,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3723,12 +3839,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3742,7 +3858,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3778,7 +3894,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3791,22 +3907,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3839,12 +3955,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3858,7 +3974,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3894,7 +4010,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3907,22 +4023,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3955,12 +4071,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3974,7 +4090,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4010,7 +4126,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4023,22 +4139,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4071,12 +4187,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4090,7 +4206,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4126,7 +4242,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4139,22 +4255,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4187,12 +4303,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4206,7 +4322,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4242,7 +4358,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4255,22 +4371,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4303,12 +4419,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4322,7 +4438,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4358,7 +4474,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4371,22 +4487,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4419,12 +4535,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4438,7 +4554,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4474,7 +4590,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4603,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4497,7 +4613,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4535,12 +4651,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4554,7 +4670,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4590,35 +4706,35 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4651,12 +4767,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4670,7 +4786,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4695,7 +4811,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4706,77 +4822,73 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4902,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4800,107 +4912,99 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4914,7 +5018,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4924,17 +5028,17 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4944,87 +5048,79 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5038,7 +5134,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5048,17 +5144,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5068,45 +5164,41 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5139,12 +5231,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5158,7 +5250,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5194,35 +5286,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5255,12 +5347,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5274,7 +5366,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5310,35 +5402,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5371,12 +5463,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5390,7 +5482,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5426,35 +5518,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5487,12 +5579,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5506,7 +5598,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5531,7 +5623,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5542,35 +5634,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5603,12 +5695,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5622,7 +5714,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5658,35 +5750,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5719,12 +5811,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5738,7 +5830,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5774,35 +5866,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5835,12 +5927,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5854,47 +5946,2911 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
+      <c r="X63" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
+      <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AD46" s="2" t="inlineStr">
-        <is>
-          <t>2/9</t>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-operations.xlsx
+++ b/data/export/2026-10-05-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:AD77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1883,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1916,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1940,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1960,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2003,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2036,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2060,17 +2068,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2080,17 +2088,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2195,7 +2203,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2210,7 +2218,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2315,7 +2323,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2392,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2512,7 +2520,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2632,7 +2640,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2686,7 +2694,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2760,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2806,7 +2814,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2880,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2992,7 +3000,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3036,12 +3044,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3112,7 +3120,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3156,87 +3164,83 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3250,7 +3254,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3260,17 +3264,17 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3280,87 +3284,79 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3374,7 +3370,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3384,22 +3380,22 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3409,12 +3405,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3423,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3437,7 +3433,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3457,24 +3453,24 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3484,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3498,7 +3494,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3523,22 +3519,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3551,52 +3547,56 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3628,33 +3628,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3667,24 +3671,24 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3697,24 +3701,24 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3724,7 +3728,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3738,7 +3742,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3773,12 +3777,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3795,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3801,7 +3805,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3811,40 +3815,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3858,7 +3866,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3868,33 +3876,37 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3919,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3917,7 +3929,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3927,32 +3939,36 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3960,7 +3976,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3974,7 +3990,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3984,33 +4000,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4023,52 +4043,56 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4076,7 +4100,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4090,7 +4114,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4100,17 +4124,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4120,13 +4144,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4139,60 +4167,64 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4206,7 +4238,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4216,33 +4248,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4291,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4265,7 +4301,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4303,12 +4339,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4322,7 +4358,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4371,7 +4407,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4381,7 +4417,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4419,12 +4455,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4438,7 +4474,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4487,7 +4523,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4497,7 +4533,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4535,12 +4571,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4554,7 +4590,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4603,22 +4639,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4651,12 +4687,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4670,7 +4706,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4719,32 +4755,32 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq46，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4772,7 +4808,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4780,13 +4816,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4835,22 +4883,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4888,7 +4936,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4902,7 +4950,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4951,22 +4999,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4999,12 +5047,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5018,7 +5066,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5067,7 +5115,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5077,7 +5125,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5115,12 +5163,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5134,7 +5182,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5183,7 +5231,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5193,7 +5241,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5231,12 +5279,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5250,7 +5298,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5299,7 +5347,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5309,7 +5357,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5347,12 +5395,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5366,7 +5414,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5415,7 +5463,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5425,7 +5473,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5468,7 +5516,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5482,7 +5530,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5531,7 +5579,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5541,7 +5589,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5579,12 +5627,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5598,7 +5646,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5647,7 +5695,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5657,7 +5705,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5695,12 +5743,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5714,7 +5762,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5763,22 +5811,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5816,7 +5864,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5830,7 +5878,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5879,22 +5927,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5932,7 +5980,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5946,7 +5994,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5995,7 +6043,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6005,7 +6053,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6043,12 +6091,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6062,7 +6110,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6111,7 +6159,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6121,7 +6169,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6164,7 +6212,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6178,7 +6226,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6227,7 +6275,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6237,7 +6285,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6280,7 +6328,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6294,7 +6342,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6319,22 +6367,18 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6391,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6357,7 +6401,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6400,7 +6444,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6414,7 +6458,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6439,22 +6483,18 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6507,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6477,7 +6517,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6515,12 +6555,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6534,7 +6574,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6559,18 +6599,22 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6627,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6593,7 +6637,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6636,7 +6680,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6650,7 +6694,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6685,82 +6729,78 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6774,7 +6814,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6784,107 +6824,99 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6898,7 +6930,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6908,17 +6940,17 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6933,82 +6965,78 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7022,7 +7050,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7032,17 +7060,17 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7057,82 +7085,78 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7146,7 +7170,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7156,17 +7180,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7181,82 +7205,78 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7270,7 +7290,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7280,17 +7300,17 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7305,12 +7325,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -7323,24 +7343,24 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7353,24 +7373,24 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -7380,7 +7400,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7394,7 +7414,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7424,17 +7444,17 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7447,52 +7467,56 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>07:35</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7500,7 +7524,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7514,7 +7538,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7524,33 +7548,37 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7563,52 +7591,56 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>07:40</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7616,7 +7648,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7630,7 +7662,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7640,17 +7672,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7665,12 +7697,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7683,60 +7715,64 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>07:55</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7750,7 +7786,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7760,33 +7796,37 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7799,60 +7839,64 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7866,7 +7910,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7876,33 +7920,37 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7963,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7925,7 +7973,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7935,32 +7983,36 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7968,7 +8020,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7982,7 +8034,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7992,17 +8044,17 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8017,12 +8069,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8087,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8045,7 +8097,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8088,7 +8140,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8102,7 +8154,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8127,22 +8179,18 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8203,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8165,7 +8213,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8175,40 +8223,44 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8222,7 +8274,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8232,33 +8284,37 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8327,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8281,7 +8337,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8319,12 +8375,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8338,7 +8394,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8363,22 +8419,18 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -8391,22 +8443,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8439,12 +8491,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8458,7 +8510,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8494,7 +8546,7 @@
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8559,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8517,7 +8569,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8560,7 +8612,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8574,7 +8626,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8609,12 +8661,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8679,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8637,7 +8689,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8675,12 +8727,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8694,7 +8746,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8729,12 +8781,12 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8799,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8757,7 +8809,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8795,12 +8847,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8814,7 +8866,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8850,7 +8902,831 @@
       <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-operations.xlsx
+++ b/data/export/2026-10-05-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD77"/>
+  <dimension ref="A1:AD93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2017,24 +2017,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2164,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2188,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2284,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2308,17 +2316,17 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2328,13 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2367,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2400,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2424,27 +2440,27 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2487,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2520,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2544,32 +2564,32 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2640,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2760,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2799,7 +2819,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2880,7 +2900,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2919,7 +2939,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2934,7 +2954,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3020,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3120,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3169,12 +3189,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>3/10</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3260,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3284,13 +3304,17 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3380,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3400,87 +3424,83 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3494,7 +3514,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3504,107 +3524,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3618,7 +3634,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3628,107 +3644,103 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3742,7 +3754,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3752,22 +3764,22 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3777,82 +3789,78 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3866,7 +3874,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3876,22 +3884,22 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3901,12 +3909,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3919,24 +3927,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3949,24 +3957,24 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3976,7 +3984,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3990,7 +3998,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4025,12 +4033,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4043,24 +4051,24 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4073,34 +4081,34 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4114,7 +4122,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4139,22 +4147,22 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4167,24 +4175,24 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4197,24 +4205,24 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4224,7 +4232,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4238,7 +4246,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4273,12 +4281,12 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4291,60 +4299,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4358,7 +4370,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4368,33 +4380,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4407,60 +4423,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4474,7 +4494,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4484,33 +4504,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4523,60 +4547,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4590,7 +4618,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4600,33 +4628,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4639,60 +4671,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4706,7 +4742,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4716,33 +4752,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4795,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4765,7 +4805,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4775,40 +4815,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq46，推进8站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4816,25 +4860,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>物理seq23（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4844,33 +4876,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4883,60 +4919,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4950,7 +4990,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4960,33 +5000,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4999,60 +5043,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5066,7 +5114,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5076,33 +5124,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5167,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5125,7 +5177,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5135,40 +5187,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5182,7 +5238,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5192,17 +5248,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5212,13 +5268,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5291,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5241,7 +5301,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5251,12 +5311,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -5279,12 +5339,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5292,13 +5352,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
       <c r="T40" s="2" t="inlineStr"/>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5334,7 +5406,7 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5347,60 +5419,64 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5414,7 +5490,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5424,33 +5500,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5463,60 +5543,64 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5530,7 +5614,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5540,17 +5624,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5560,13 +5644,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5667,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5589,7 +5677,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5627,12 +5715,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5646,7 +5734,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5682,7 +5770,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5783,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5705,7 +5793,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5743,12 +5831,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5762,7 +5850,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5798,7 +5886,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5899,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5821,7 +5909,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5859,12 +5947,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5878,7 +5966,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5914,7 +6002,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5927,7 +6015,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5937,7 +6025,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5975,12 +6063,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5994,7 +6082,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6030,7 +6118,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6043,22 +6131,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6091,12 +6179,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6110,7 +6198,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6146,7 +6234,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6159,22 +6247,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6207,12 +6295,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6226,7 +6314,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6262,7 +6350,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6275,22 +6363,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6323,12 +6411,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6342,7 +6430,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6378,7 +6466,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6391,22 +6479,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6444,7 +6532,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6458,7 +6546,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6494,7 +6582,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6595,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6517,7 +6605,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6555,12 +6643,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6574,7 +6662,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6599,22 +6687,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6711,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6637,7 +6721,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6680,7 +6764,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6694,7 +6778,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6719,22 +6803,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6827,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6757,7 +6837,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6795,12 +6875,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6814,7 +6894,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6850,7 +6930,7 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6943,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6873,7 +6953,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6916,7 +6996,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6930,7 +7010,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6955,22 +7035,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6983,7 +7059,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6993,7 +7069,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -7036,7 +7112,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7050,7 +7126,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7085,12 +7161,12 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7103,22 +7179,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7156,7 +7232,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7170,7 +7246,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7205,12 +7281,12 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7223,22 +7299,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7271,12 +7347,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7290,7 +7366,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7315,92 +7391,84 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>123.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7414,7 +7482,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7424,17 +7492,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7444,87 +7512,83 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7538,7 +7602,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7548,17 +7612,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7573,82 +7637,78 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7662,7 +7722,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7672,17 +7732,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7697,82 +7757,78 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7786,7 +7842,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7796,17 +7852,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7821,82 +7877,78 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7910,7 +7962,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7920,17 +7972,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7945,82 +7997,78 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8034,7 +8082,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8044,17 +8092,17 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8069,40 +8117,40 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8135,12 +8183,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8154,7 +8202,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8190,77 +8238,73 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8274,7 +8318,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8284,17 +8328,17 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8304,45 +8348,45 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8375,12 +8419,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8394,7 +8438,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8419,46 +8463,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8491,12 +8539,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8510,7 +8558,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8535,18 +8583,22 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -8559,52 +8611,56 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8612,7 +8668,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8626,7 +8682,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8636,37 +8692,37 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8684,47 +8740,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8732,7 +8792,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8746,7 +8806,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8756,32 +8816,32 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
@@ -8799,60 +8859,64 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8866,7 +8930,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8876,33 +8940,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8920,47 +8988,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8968,7 +9040,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8982,7 +9054,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8992,17 +9064,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -9035,7 +9107,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9045,7 +9117,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9055,40 +9127,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9102,7 +9178,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9112,33 +9188,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9231,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9161,7 +9241,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9171,32 +9251,36 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9204,7 +9288,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9218,7 +9302,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9228,17 +9312,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9253,12 +9337,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9355,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9281,7 +9365,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9319,12 +9403,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9338,7 +9422,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9368,17 +9452,13 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9471,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9401,7 +9481,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9411,40 +9491,44 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9458,7 +9542,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9468,33 +9552,37 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9507,60 +9595,64 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9574,7 +9666,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9584,33 +9676,37 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9623,60 +9719,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9690,41 +9790,1945 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>69分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>09:17</t>
         </is>
       </c>
-      <c r="W77" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X77" s="2" t="inlineStr">
+      <c r="X87" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y77" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z77" s="2" t="inlineStr">
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
+      <c r="AA87" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
+      <c r="AB87" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC77" s="2" t="inlineStr"/>
-      <c r="AD77" s="2" t="inlineStr">
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr">
         <is>
           <t>—/14</t>
         </is>

--- a/data/export/2026-10-05-operations.xlsx
+++ b/data/export/2026-10-05-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2832,17 +2832,17 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3328,17 +3328,17 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,17 +3948,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6180,17 +6180,17 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6676,17 +6676,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7048,17 +7048,17 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7668,17 +7668,17 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8412,17 +8412,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8660,17 +8660,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8961,24 +8961,24 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
     </row>
@@ -9075,32 +9075,36 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9108,7 +9112,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9132,17 +9136,17 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -9152,12 +9156,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
@@ -9195,32 +9199,36 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9228,7 +9236,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9252,17 +9260,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -9272,17 +9280,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -9315,32 +9323,36 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9348,7 +9360,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9372,17 +9384,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9392,17 +9404,17 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9588,7 +9600,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9632,12 +9644,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9766,7 +9778,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9972,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10004,17 +10016,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10274,7 @@
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10386,7 +10398,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10840,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10872,12 +10884,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
@@ -10952,7 +10964,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11208,7 +11220,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11252,12 +11264,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>120.7</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
@@ -11452,7 +11464,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11506,7 +11518,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11588,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11620,7 +11632,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11630,7 +11642,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11836,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11948,7 +11960,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12072,7 +12084,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12320,7 +12332,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12369,12 +12381,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -12444,7 +12456,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12498,7 +12510,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12700,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12986,7 +12998,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13192,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13234,7 +13246,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13370,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13440,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13472,17 +13484,17 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -13924,7 +13936,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13978,7 +13990,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14184,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14216,12 +14228,12 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
@@ -14420,7 +14432,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14540,7 +14552,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14584,12 +14596,12 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>120.7</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
@@ -14788,7 +14800,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14832,7 +14844,7 @@
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
@@ -14842,7 +14854,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -14912,7 +14924,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14966,7 +14978,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -15036,7 +15048,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15284,7 +15296,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15408,7 +15420,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15656,7 +15668,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15710,7 +15722,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -15958,7 +15970,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -16082,7 +16094,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -16152,7 +16164,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16206,7 +16218,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -17028,7 +17040,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17082,7 +17094,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17288,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17320,7 +17332,7 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
@@ -17330,7 +17342,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -17524,7 +17536,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17702,7 +17714,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18086,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18780,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18812,12 +18824,12 @@
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC148" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD148" s="2" t="inlineStr">
@@ -18892,7 +18904,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18941,12 +18953,12 @@
       </c>
       <c r="AC149" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -19016,7 +19028,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19140,7 +19152,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19184,12 +19196,12 @@
       </c>
       <c r="AB151" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC151" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>120.7</t>
         </is>
       </c>
       <c r="AD151" s="2" t="inlineStr">
@@ -19264,7 +19276,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19318,7 +19330,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -19388,7 +19400,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19512,7 +19524,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19566,7 +19578,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19648,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19680,17 +19692,17 @@
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -19760,7 +19772,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19814,7 +19826,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19896,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19938,7 +19950,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -20132,7 +20144,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20500,7 +20512,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20554,7 +20566,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -21492,7 +21504,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21589,24 +21601,24 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr"/>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -21616,7 +21628,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21665,12 +21677,12 @@
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -21703,32 +21715,36 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N172" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -21736,7 +21752,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21760,17 +21776,17 @@
       </c>
       <c r="X172" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA172" s="2" t="inlineStr">
@@ -21780,7 +21796,7 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
@@ -21790,7 +21806,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -21860,7 +21876,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21947,32 +21963,36 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N174" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -21980,7 +22000,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22004,17 +22024,17 @@
       </c>
       <c r="X174" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y174" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z174" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA174" s="2" t="inlineStr">
@@ -22024,12 +22044,12 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
@@ -22067,12 +22087,12 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
@@ -22100,7 +22120,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22108,10 +22128,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R175" s="2" t="inlineStr"/>
-      <c r="S175" s="2" t="inlineStr"/>
-      <c r="T175" s="2" t="inlineStr"/>
-      <c r="U175" s="2" t="inlineStr"/>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V175" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22154,7 +22190,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -22187,32 +22223,36 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N176" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22220,7 +22260,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22244,17 +22284,17 @@
       </c>
       <c r="X176" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z176" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA176" s="2" t="inlineStr">
@@ -22264,17 +22304,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -22307,32 +22347,36 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N177" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -22340,7 +22384,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22364,17 +22408,17 @@
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA177" s="2" t="inlineStr">
@@ -22384,12 +22428,12 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>120.7</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
@@ -22460,7 +22504,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22514,7 +22558,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -22547,12 +22591,12 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq53，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
@@ -22580,18 +22624,30 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
           <t>20:11</t>
         </is>
       </c>
-      <c r="Q179" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="R179" s="2" t="inlineStr"/>
-      <c r="S179" s="2" t="inlineStr"/>
       <c r="T179" s="2" t="inlineStr"/>
-      <c r="U179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V179" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -22634,7 +22690,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -22700,7 +22756,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22820,7 +22876,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22874,7 +22930,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -22940,7 +22996,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23060,7 +23116,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23180,7 +23236,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23234,7 +23290,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -23300,7 +23356,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23602,7 +23658,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -24218,7 +24274,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -24536,7 +24592,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24585,7 +24641,7 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
@@ -24838,7 +24894,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -24908,7 +24964,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24952,17 +25008,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -25524,7 +25580,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25568,7 +25624,7 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
@@ -25578,7 +25634,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -25648,7 +25704,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25692,17 +25748,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -25772,7 +25828,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25816,17 +25872,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -25950,7 +26006,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -26322,7 +26378,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -26392,7 +26448,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26441,7 +26497,7 @@
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
@@ -26640,7 +26696,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26684,17 +26740,17 @@
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -27012,7 +27068,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27056,7 +27112,7 @@
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
@@ -27066,7 +27122,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27192,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27180,17 +27236,17 @@
       </c>
       <c r="AB216" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27316,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27304,17 +27360,17 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -27562,7 +27618,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -27632,7 +27688,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27681,7 +27737,7 @@
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
@@ -27756,7 +27812,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27800,17 +27856,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -27934,7 +27990,7 @@
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28060,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28048,7 +28104,7 @@
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC223" s="2" t="inlineStr">
@@ -28058,7 +28114,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -28252,7 +28308,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28296,17 +28352,17 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -28376,7 +28432,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28420,17 +28476,17 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28610,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -28624,7 +28680,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28668,17 +28724,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -28802,7 +28858,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -29244,7 +29300,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29288,17 +29344,17 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -29492,7 +29548,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29536,17 +29592,17 @@
       </c>
       <c r="AB235" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -29616,7 +29672,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29665,7 +29721,7 @@
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
@@ -29794,7 +29850,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -30042,7 +30098,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -30112,7 +30168,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30156,17 +30212,17 @@
       </c>
       <c r="AB240" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -30360,7 +30416,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30404,7 +30460,7 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
@@ -30414,7 +30470,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -30856,7 +30912,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30905,7 +30961,7 @@
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
@@ -30980,7 +31036,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31024,17 +31080,17 @@
       </c>
       <c r="AB247" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -31104,7 +31160,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31148,17 +31204,17 @@
       </c>
       <c r="AB248" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -31282,7 +31338,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -31352,7 +31408,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -31396,17 +31452,17 @@
       </c>
       <c r="AB250" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -31530,7 +31586,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -31724,7 +31780,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31768,17 +31824,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -31972,7 +32028,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32016,7 +32072,7 @@
       </c>
       <c r="AB255" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC255" s="2" t="inlineStr">
@@ -32026,7 +32082,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -32588,7 +32644,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32632,17 +32688,17 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -32712,7 +32768,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32756,17 +32812,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -32836,7 +32892,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32885,7 +32941,7 @@
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
@@ -32960,7 +33016,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33004,17 +33060,17 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33194,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -33258,7 +33314,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -33448,7 +33504,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33492,17 +33548,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33696,7 +33752,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33740,7 +33796,7 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
@@ -33750,7 +33806,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34275,32 +34331,36 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr"/>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N274" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O274" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34308,7 +34368,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34332,17 +34392,17 @@
       </c>
       <c r="X274" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z274" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA274" s="2" t="inlineStr">
@@ -34352,17 +34412,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -34405,24 +34465,24 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr"/>
       <c r="M275" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N275" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O275" s="2" t="inlineStr">
@@ -34432,7 +34492,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34481,7 +34541,7 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -34639,32 +34699,36 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr"/>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N277" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O277" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34672,7 +34736,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34696,17 +34760,17 @@
       </c>
       <c r="X277" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z277" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA277" s="2" t="inlineStr">
@@ -34716,17 +34780,17 @@
       </c>
       <c r="AB277" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -34759,32 +34823,36 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr"/>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N278" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O278" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -34792,7 +34860,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34816,17 +34884,17 @@
       </c>
       <c r="X278" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z278" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA278" s="2" t="inlineStr">
@@ -34836,17 +34904,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -34879,32 +34947,36 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N279" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O279" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -34912,7 +34984,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34936,17 +35008,17 @@
       </c>
       <c r="X279" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA279" s="2" t="inlineStr">
@@ -34956,17 +35028,17 @@
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -34999,32 +35071,36 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr"/>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N280" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O280" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -35032,7 +35108,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35056,17 +35132,17 @@
       </c>
       <c r="X280" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z280" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA280" s="2" t="inlineStr">
@@ -35076,7 +35152,7 @@
       </c>
       <c r="AB280" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC280" s="2" t="inlineStr">
@@ -35086,7 +35162,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -35152,7 +35228,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35196,17 +35272,17 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -35272,7 +35348,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35316,17 +35392,17 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-05-operations.xlsx
+++ b/data/export/2026-10-05-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1220,17 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3576,17 +3576,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6056,17 +6056,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6924,17 +6924,17 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7792,17 +7792,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8040,17 +8040,17 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8908,17 +8908,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9156,17 +9156,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -9333,24 +9333,24 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
     </row>
@@ -9447,32 +9447,36 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9480,7 +9484,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9504,17 +9508,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9524,17 +9528,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -9567,32 +9571,36 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9600,7 +9608,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9624,17 +9632,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9644,17 +9652,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>4/10</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10034,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10352,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10388,17 +10396,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10530,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10972,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11150,7 +11158,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11406,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11472,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11766,7 +11774,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11836,7 +11844,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11880,17 +11888,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -11960,7 +11968,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12014,7 +12022,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12092,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12128,17 +12136,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12270,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12518,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12638,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12762,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12882,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13200,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13246,7 +13254,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13502,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13750,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13944,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13980,17 +13988,17 @@
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14440,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14730,7 +14738,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -14924,7 +14932,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15048,7 +15056,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15092,17 +15100,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -15226,7 +15234,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15304,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15340,17 +15348,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15428,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15474,7 +15482,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -15598,7 +15606,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15730,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15854,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16172,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16218,7 +16226,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -16846,7 +16854,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16978,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -17218,7 +17226,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -17466,7 +17474,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17544,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17580,17 +17588,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -17838,7 +17846,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17970,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -18458,7 +18466,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18722,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -19082,7 +19090,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -19400,7 +19408,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19444,17 +19452,17 @@
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -19578,7 +19586,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19710,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -19772,7 +19780,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19826,7 +19834,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -19896,7 +19904,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19940,17 +19948,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -20144,7 +20152,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20446,7 +20454,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -20512,7 +20520,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20690,7 +20698,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -20810,7 +20818,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -21058,7 +21066,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21190,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21302,7 +21310,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21512,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21558,7 +21566,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21938,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -22190,7 +22198,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22322,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22604,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq53，推进25站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
@@ -22624,7 +22632,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22690,7 +22698,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -22723,32 +22731,36 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -22756,7 +22768,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22780,17 +22792,17 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA180" s="2" t="inlineStr">
@@ -22800,17 +22812,17 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -22843,32 +22855,36 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N181" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -22876,7 +22892,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22900,17 +22916,17 @@
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA181" s="2" t="inlineStr">
@@ -22920,17 +22936,17 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -22963,32 +22979,36 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -22996,7 +23016,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23020,17 +23040,17 @@
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA182" s="2" t="inlineStr">
@@ -23040,17 +23060,17 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -23116,7 +23136,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23236,7 +23256,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23356,7 +23376,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23410,7 +23430,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -25580,7 +25600,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25704,7 +25724,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25748,12 +25768,12 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -27068,7 +27088,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27316,7 +27336,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27360,12 +27380,12 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
@@ -28060,7 +28080,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28308,7 +28328,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28352,12 +28372,12 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
@@ -28680,7 +28700,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -29548,7 +29568,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -30416,7 +30436,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -31160,7 +31180,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31204,12 +31224,12 @@
       </c>
       <c r="AB248" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
@@ -31408,7 +31428,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -32028,7 +32048,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32768,7 +32788,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32812,12 +32832,12 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
@@ -33016,7 +33036,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33752,7 +33772,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -34736,7 +34756,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34780,12 +34800,12 @@
       </c>
       <c r="AB277" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
@@ -34860,7 +34880,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -35108,7 +35128,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35195,32 +35215,36 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N281" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O281" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35228,7 +35252,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35252,17 +35276,17 @@
       </c>
       <c r="X281" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA281" s="2" t="inlineStr">
@@ -35272,12 +35296,12 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35348,7 +35372,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
